--- a/dados_excel/teams_infos.xlsx
+++ b/dados_excel/teams_infos.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z103"/>
+  <dimension ref="A1:Z106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="6.5" customWidth="1" style="3" min="1" max="1"/>
@@ -5869,6 +5869,167 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2841</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Minerva Artemis</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ARTMS</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>UFRJ</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>assets\team-logos\ufrj_minerva.png</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/minervaesports/</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>131732</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>fdc725</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2842</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>A2E UFF Shadows</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>A2E S</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Universidade Federal Fluminense</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>UFF</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>assets\team-logos\a2e_uff.png</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a2euff/</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>7617ad</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>a388f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2843</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sheriff IFF</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SHF</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Instituto Federal de Educação, Ciência e Tecnologia Fluminense</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>IFF</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>assets\team-logos\sheriff.png</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>f9b70b</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>775e25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
